--- a/src/product/data/Announcement_Field_Values.xlsx
+++ b/src/product/data/Announcement_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AutomationFramework\govgrants-playwright-automation\src\product\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jenkins_Playwright_FW\govgrants-playwright-automation\src\product\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE393CD-335A-4285-97AB-142EF35C5E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="795" firstSheet="28" activeTab="29" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="795" firstSheet="13" activeTab="14" xr2:uid="{D00E3ABE-F797-4780-AECA-E481BEE93CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="DirectedAnnouncement_Admin" sheetId="44" r:id="rId1"/>
